--- a/Liberacao/Liberacao-modelo.xlsx
+++ b/Liberacao/Liberacao-modelo.xlsx
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="365">
   <si>
     <t xml:space="preserve">Liberação e produto não conforme — Como usar esta planilha</t>
   </si>
@@ -981,7 +981,7 @@
     <t xml:space="preserve">2027-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Mussarela, nota de 17/03</t>
+    <t xml:space="preserve">Muçarela, nota de 17/03</t>
   </si>
   <si>
     <t xml:space="preserve">Insumo fora de temperatura</t>
@@ -1038,16 +1038,13 @@
     <t xml:space="preserve">Pedido 5431</t>
   </si>
   <si>
-    <t xml:space="preserve">Atendente líder</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cliente atendido em 20/03: pizza nova entregue em 35 minutos.</t>
   </si>
   <si>
     <t xml:space="preserve">Pedido 5440</t>
   </si>
   <si>
-    <t xml:space="preserve">RNC 2027-07</t>
+    <t xml:space="preserve">RNC 2027-03</t>
   </si>
   <si>
     <t xml:space="preserve">Liberações: registradas, a rever</t>
@@ -1071,7 +1068,7 @@
     <t xml:space="preserve">Analista da Qualidade, com o laudo do lote. Liberação com verificação pendente: só com a autorização do gerente industrial e o aceite do cliente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordenador da Qualidade. Refugo acima de 500 kg e recolhimento no cliente: gerente industrial e gerente comercial.</t>
+    <t xml:space="preserve">Coordenador da Qualidade. Retrabalho na linha: líder do turno. Devolução de insumo ao fornecedor: gerente de Suprimentos. Refugo acima de 500 kg e recolhimento no cliente: gerente industrial e gerente comercial.</t>
   </si>
   <si>
     <t xml:space="preserve">Lotes 136 a 143, de 17 a 26/05/2027, lidos em 28/05/2027.</t>
@@ -1113,7 +1110,7 @@
     <t xml:space="preserve">Retido</t>
   </si>
   <si>
-    <t xml:space="preserve">Espessura acima do critério nas duas bobinas.</t>
+    <t xml:space="preserve">Espessura acima do critério nas duas bobinas. Retido em 20/05; liberado em 21/05, com a concessão do cliente B.</t>
   </si>
   <si>
     <t xml:space="preserve">Lote 141</t>
@@ -1194,7 +1191,7 @@
     <t xml:space="preserve">300 kg</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente comercial</t>
+    <t xml:space="preserve">Gerente industrial e gerente comercial</t>
   </si>
   <si>
     <t xml:space="preserve">Cliente A informado em 24/05. Bobina recolhida e reposta em 26/05.</t>
@@ -1856,11 +1853,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="0"/>
-        <c:axId val="50765640"/>
-        <c:axId val="45289809"/>
+        <c:axId val="39362509"/>
+        <c:axId val="59297971"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50765640"/>
+        <c:axId val="39362509"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1892,7 +1889,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45289809"/>
+        <c:crossAx val="59297971"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1900,7 +1897,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45289809"/>
+        <c:axId val="59297971"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1940,7 +1937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50765640"/>
+        <c:crossAx val="39362509"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8740,10 +8737,10 @@
         <v>89</v>
       </c>
       <c r="J30" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="K30" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>300</v>
       </c>
       <c r="L30" s="37"/>
       <c r="M30" s="35" t="n">
@@ -8770,7 +8767,7 @@
         <v>46466</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>276</v>
@@ -8799,7 +8796,7 @@
         <v>28</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P31" s="22" t="str">
         <f aca="false">IF(E31="","",IF(I31="","Aberto",IF(M31="","Em tratamento","Encerrado")))</f>
@@ -8968,7 +8965,7 @@
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -8991,7 +8988,7 @@
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -9060,7 +9057,7 @@
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -9283,7 +9280,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="32" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -9305,7 +9302,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="32" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
@@ -9327,7 +9324,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="32" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -9349,7 +9346,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="32" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -9364,14 +9361,14 @@
       <c r="P7" s="32"/>
       <c r="Q7" s="32"/>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>239</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -9393,7 +9390,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -9415,7 +9412,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="32" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -9499,10 +9496,10 @@
         <v>46524</v>
       </c>
       <c r="C14" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>314</v>
       </c>
       <c r="E14" s="37" t="n">
         <v>12</v>
@@ -9539,10 +9536,10 @@
         <v>46525</v>
       </c>
       <c r="C15" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>316</v>
       </c>
       <c r="E15" s="37" t="n">
         <v>12</v>
@@ -9569,7 +9566,7 @@
         <v>297</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
@@ -9583,10 +9580,10 @@
         <v>46526</v>
       </c>
       <c r="C16" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>319</v>
       </c>
       <c r="E16" s="37" t="n">
         <v>12</v>
@@ -9648,12 +9645,12 @@
         <v>119</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L17" s="7"/>
       <c r="M17" s="37"/>
       <c r="N17" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
@@ -9662,7 +9659,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="35" t="n">
         <v>46527</v>
       </c>
@@ -9670,7 +9667,7 @@
         <v>151</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E18" s="37" t="n">
         <v>12</v>
@@ -9686,16 +9683,18 @@
         <v>Com desvio</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="J18" s="7"/>
+        <v>322</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="37" t="s">
         <v>150</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
@@ -9709,10 +9708,10 @@
         <v>46528</v>
       </c>
       <c r="C19" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>326</v>
       </c>
       <c r="E19" s="37" t="n">
         <v>12</v>
@@ -9749,10 +9748,10 @@
         <v>46531</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>327</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>328</v>
       </c>
       <c r="E20" s="37" t="n">
         <v>12</v>
@@ -9777,7 +9776,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="37"/>
       <c r="N20" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
@@ -9791,10 +9790,10 @@
         <v>46533</v>
       </c>
       <c r="C21" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>331</v>
       </c>
       <c r="E21" s="37" t="n">
         <v>12</v>
@@ -9818,10 +9817,10 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -9908,19 +9907,19 @@
         <v>46518</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E25" s="36" t="s">
         <v>334</v>
       </c>
-      <c r="E25" s="36" t="s">
+      <c r="F25" s="37" t="s">
         <v>335</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>336</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>195</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I25" s="37" t="s">
         <v>85</v>
@@ -9954,19 +9953,19 @@
         <v>46519</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>152</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G26" s="37" t="s">
         <v>195</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I26" s="37" t="s">
         <v>81</v>
@@ -9983,7 +9982,7 @@
         <v>620</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P26" s="22" t="str">
         <f aca="false">IF(E26="","",IF(I26="","Aberto",IF(M26="","Em tratamento","Encerrado")))</f>
@@ -10002,19 +10001,19 @@
         <v>46521</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E27" s="36" t="s">
         <v>152</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G27" s="37" t="s">
         <v>195</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I27" s="37" t="s">
         <v>85</v>
@@ -10048,19 +10047,19 @@
         <v>46525</v>
       </c>
       <c r="D28" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="F28" s="37" t="s">
         <v>343</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>344</v>
       </c>
       <c r="G28" s="37" t="s">
         <v>195</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I28" s="37" t="s">
         <v>85</v>
@@ -10094,7 +10093,7 @@
         <v>46527</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E29" s="36" t="s">
         <v>152</v>
@@ -10106,7 +10105,7 @@
         <v>155</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I29" s="37" t="s">
         <v>83</v>
@@ -10115,7 +10114,7 @@
         <v>157</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L29" s="37"/>
       <c r="M29" s="35" t="n">
@@ -10136,19 +10135,19 @@
     </row>
     <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C30" s="35" t="n">
         <v>46531</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>152</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>198</v>
@@ -10158,10 +10157,10 @@
         <v>89</v>
       </c>
       <c r="J30" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="K30" s="7" t="s">
         <v>351</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>352</v>
       </c>
       <c r="L30" s="37"/>
       <c r="M30" s="35"/>
@@ -10180,31 +10179,31 @@
     </row>
     <row r="31" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C31" s="35" t="n">
         <v>46532</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E31" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="E31" s="36" t="s">
+      <c r="F31" s="37" t="s">
         <v>355</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>356</v>
       </c>
       <c r="G31" s="37" t="s">
         <v>193</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I31" s="37" t="s">
         <v>87</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="37"/>
@@ -10226,31 +10225,31 @@
     </row>
     <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C32" s="35" t="n">
         <v>46533</v>
       </c>
       <c r="D32" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E32" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="E32" s="36" t="s">
-        <v>360</v>
-      </c>
       <c r="F32" s="37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>195</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I32" s="37" t="s">
         <v>79</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="37"/>
@@ -10268,21 +10267,21 @@
         <v>Falta a reverificação</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C33" s="35" t="n">
         <v>46533</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E33" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>364</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>365</v>
       </c>
       <c r="G33" s="37" t="s">
         <v>198</v>
@@ -10292,7 +10291,7 @@
         <v>89</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>157</v>
+        <v>350</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="37"/>
@@ -10468,7 +10467,7 @@
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -10491,7 +10490,7 @@
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -10560,7 +10559,7 @@
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
